--- a/projekt.xlsx
+++ b/projekt.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Szoke-lena\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szoke.lena\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8289BC0C-5729-4884-9FCD-A3BAA80F869D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC51FA9-16AF-4F5E-8066-1C22FEB2F31F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{5F58B20C-3803-4A9F-8C1B-4C99A4236629}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{5F58B20C-3803-4A9F-8C1B-4C99A4236629}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
   <si>
     <t>Jegyek</t>
   </si>
@@ -75,16 +75,55 @@
     <t>Fogyatékkal élők részére</t>
   </si>
   <si>
-    <t>Óvodás csoport</t>
-  </si>
-  <si>
-    <t>Diák csoport</t>
-  </si>
-  <si>
     <t>Felnőtt csoport</t>
   </si>
   <si>
     <t>Nyugdíjas csoport</t>
+  </si>
+  <si>
+    <t>Delfin bemutató</t>
+  </si>
+  <si>
+    <t>Pingvinek etetése</t>
+  </si>
+  <si>
+    <t>Denevérek etetése</t>
+  </si>
+  <si>
+    <t>Ragadozók etetése</t>
+  </si>
+  <si>
+    <t>Fókatréning</t>
+  </si>
+  <si>
+    <t>Kertészeti bemutató</t>
+  </si>
+  <si>
+    <t>Óriásvidrák etetése</t>
+  </si>
+  <si>
+    <t>Vadállatmentésről előadás</t>
+  </si>
+  <si>
+    <t>Kisállatkerti állatok bemutatása</t>
+  </si>
+  <si>
+    <t>Bonsai bemutató</t>
+  </si>
+  <si>
+    <t>Madár bemutató</t>
+  </si>
+  <si>
+    <t>Hiéna comedy</t>
+  </si>
+  <si>
+    <t>Ingyenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Csoport: min 5 fő </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diák csoport </t>
   </si>
 </sst>
 </file>
@@ -104,15 +143,87 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB74D9B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99FFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -120,19 +231,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCC66"/>
+      <color rgb="FFFF9933"/>
+      <color rgb="FF008080"/>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FF99FFCC"/>
+      <color rgb="FFCC6600"/>
+      <color rgb="FF99CCFF"/>
+      <color rgb="FFB74D9B"/>
+      <color rgb="FF993366"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -441,125 +624,299 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3759D5DD-9019-4A39-8F5A-0A1CF0D86C3B}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1">
         <v>3600</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D3" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1">
         <v>3600</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D4" s="4">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1">
         <v>6000</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D5" s="4">
+        <v>0.5625</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D8" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.64583333333333404</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>4000</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1">
-        <v>4000</v>
+      <c r="D10" s="4">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E7:K7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/projekt.xlsx
+++ b/projekt.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\szoke.lena\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC51FA9-16AF-4F5E-8066-1C22FEB2F31F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9623FDA6-41B4-4211-A7F1-E93FA180AB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7980" xr2:uid="{5F58B20C-3803-4A9F-8C1B-4C99A4236629}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
   <si>
     <t>Jegyek</t>
   </si>
@@ -33,6 +44,9 @@
     <t>Ár</t>
   </si>
   <si>
+    <t>Program</t>
+  </si>
+  <si>
     <t>Hétfő</t>
   </si>
   <si>
@@ -54,76 +68,61 @@
     <t>Vasárnap</t>
   </si>
   <si>
-    <t>Program</t>
-  </si>
-  <si>
     <t>3 év alatt</t>
   </si>
   <si>
+    <t>Ingyenes</t>
+  </si>
+  <si>
+    <t>Kertészeti bemutató</t>
+  </si>
+  <si>
+    <t>Pingvinek etetése</t>
+  </si>
+  <si>
     <t>Gyerek (3-14 év)</t>
   </si>
   <si>
+    <t>Ragadozók etetése</t>
+  </si>
+  <si>
     <t>Diák</t>
   </si>
   <si>
+    <t>Bonsai bemutató</t>
+  </si>
+  <si>
+    <t>Madár bemutató</t>
+  </si>
+  <si>
     <t>Felnőtt</t>
   </si>
   <si>
+    <t>Óriásvidrák etetése</t>
+  </si>
+  <si>
+    <t>Vadállatmentésről előadás</t>
+  </si>
+  <si>
     <t>Nyugdíjas</t>
   </si>
   <si>
+    <t>Delfin bemutató</t>
+  </si>
+  <si>
     <t>Fogyatékkal élők részére</t>
   </si>
   <si>
-    <t>Felnőtt csoport</t>
-  </si>
-  <si>
-    <t>Nyugdíjas csoport</t>
-  </si>
-  <si>
-    <t>Delfin bemutató</t>
-  </si>
-  <si>
-    <t>Pingvinek etetése</t>
+    <t>Kisállatkerti állatok bemutatása</t>
+  </si>
+  <si>
+    <t>Hiéna comedy</t>
+  </si>
+  <si>
+    <t>Fókatréning</t>
   </si>
   <si>
     <t>Denevérek etetése</t>
-  </si>
-  <si>
-    <t>Ragadozók etetése</t>
-  </si>
-  <si>
-    <t>Fókatréning</t>
-  </si>
-  <si>
-    <t>Kertészeti bemutató</t>
-  </si>
-  <si>
-    <t>Óriásvidrák etetése</t>
-  </si>
-  <si>
-    <t>Vadállatmentésről előadás</t>
-  </si>
-  <si>
-    <t>Kisállatkerti állatok bemutatása</t>
-  </si>
-  <si>
-    <t>Bonsai bemutató</t>
-  </si>
-  <si>
-    <t>Madár bemutató</t>
-  </si>
-  <si>
-    <t>Hiéna comedy</t>
-  </si>
-  <si>
-    <t>Ingyenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Csoport: min 5 fő </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diák csoport </t>
   </si>
 </sst>
 </file>
@@ -133,7 +132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;Ft&quot;;[Red]\-#,##0\ &quot;Ft&quot;"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,22 +277,22 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -328,7 +327,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -624,14 +623,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3759D5DD-9019-4A39-8F5A-0A1CF0D86C3B}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="11" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -639,65 +638,65 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4">
         <v>0.5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>3600</v>
@@ -706,21 +705,21 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1">
         <v>3600</v>
@@ -729,30 +728,30 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1">
         <v>6000</v>
@@ -760,31 +759,31 @@
       <c r="D5" s="4">
         <v>0.5625</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1">
         <v>5000</v>
@@ -793,22 +792,22 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="14" t="s">
-        <v>18</v>
+      <c r="F6" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="14" t="s">
-        <v>18</v>
+      <c r="H6" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="I6" s="3"/>
-      <c r="J6" s="14" t="s">
-        <v>18</v>
+      <c r="J6" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="K6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1">
         <v>3000</v>
@@ -816,101 +815,81 @@
       <c r="D7" s="4">
         <v>0.60416666666666696</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2500</v>
-      </c>
+      <c r="E7" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="1"/>
       <c r="D8" s="4">
         <v>0.625</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5000</v>
-      </c>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="1"/>
       <c r="D9" s="4">
         <v>0.64583333333333404</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>22</v>
+      <c r="F9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="15" t="s">
-        <v>22</v>
+      <c r="J9" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4000</v>
-      </c>
+    <row r="10" spans="1:11">
+      <c r="B10" s="1"/>
       <c r="D10" s="4">
         <v>0.66666666666666696</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K10" s="3"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
